--- a/testdata/configurationUAT/data.xlsx
+++ b/testdata/configurationUAT/data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000"/>
+    <workbookView windowWidth="13343" windowHeight="4956"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="95">
   <si>
     <t>username</t>
   </si>
@@ -44,6 +44,9 @@
     <t>account_details_owner</t>
   </si>
   <si>
+    <t>account_details_owner2</t>
+  </si>
+  <si>
     <t>current_account_1_name</t>
   </si>
   <si>
@@ -179,6 +182,12 @@
     <t>cards_item_credit_card_number</t>
   </si>
   <si>
+    <t>auth_current_account_bban</t>
+  </si>
+  <si>
+    <t>auth_current_account_owner_name</t>
+  </si>
+  <si>
     <t>mirko.lekic@ibank</t>
   </si>
   <si>
@@ -188,93 +197,96 @@
     <t>ART02</t>
   </si>
   <si>
+    <t>STOJKA PEŠIĆ</t>
+  </si>
+  <si>
+    <t>Devizni platni račun</t>
+  </si>
+  <si>
+    <t>205-9001001027335-67</t>
+  </si>
+  <si>
+    <t>RS35 2059 0310 0388 8377 30</t>
+  </si>
+  <si>
+    <t>Tekući račun</t>
+  </si>
+  <si>
+    <t>RS35 2059 0310 0918 7915 07</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>RS35 2059 0310 0021 5320 98</t>
+  </si>
+  <si>
+    <t>Visa prepaid</t>
+  </si>
+  <si>
+    <t>4313 **** **** 5309</t>
+  </si>
+  <si>
+    <t>4431********0118</t>
+  </si>
+  <si>
+    <t>Visa revolving card</t>
+  </si>
+  <si>
+    <t>4176 **** **** 2688</t>
+  </si>
+  <si>
+    <t>4431 **** **** 0118</t>
+  </si>
+  <si>
+    <t>A vista depozitni račun</t>
+  </si>
+  <si>
+    <t>9011001198909</t>
+  </si>
+  <si>
+    <t>9011002281168</t>
+  </si>
+  <si>
+    <t>Oročeni depozit</t>
+  </si>
+  <si>
+    <t>9032023653356</t>
+  </si>
+  <si>
+    <t>9032033075822</t>
+  </si>
+  <si>
+    <t>205-9001007790944-88</t>
+  </si>
+  <si>
+    <t>Gotovinski kredit</t>
+  </si>
+  <si>
+    <t>0049034095794</t>
+  </si>
+  <si>
+    <t>Stambeni kredit</t>
+  </si>
+  <si>
+    <t>0049005022648</t>
+  </si>
+  <si>
+    <t>KOAR TGR</t>
+  </si>
+  <si>
+    <t>ULICAA</t>
+  </si>
+  <si>
+    <t>Beograd</t>
+  </si>
+  <si>
+    <t>205-9001000243808-47</t>
+  </si>
+  <si>
     <t>ANOEV OSIR</t>
   </si>
   <si>
-    <t>Devizni platni račun</t>
-  </si>
-  <si>
-    <t>.</t>
-  </si>
-  <si>
-    <t>RS35 2059 0310 0388 8377 30</t>
-  </si>
-  <si>
-    <t>Tekući račun</t>
-  </si>
-  <si>
-    <t>205-9001001027335-67</t>
-  </si>
-  <si>
-    <t>RS35 2059 0310 0918 7915 07</t>
-  </si>
-  <si>
-    <t>RS35 2059 0310 0021 5320 98</t>
-  </si>
-  <si>
-    <t>Visa prepaid</t>
-  </si>
-  <si>
-    <t>4313 **** **** 5309</t>
-  </si>
-  <si>
-    <t>4431********0118</t>
-  </si>
-  <si>
-    <t>Visa revolving card</t>
-  </si>
-  <si>
-    <t>4176 **** **** 2688</t>
-  </si>
-  <si>
-    <t>4431 **** **** 0118</t>
-  </si>
-  <si>
-    <t>A vista depozitni račun</t>
-  </si>
-  <si>
-    <t>9011001198909</t>
-  </si>
-  <si>
-    <t>9011002281168</t>
-  </si>
-  <si>
-    <t>Oročeni depozit</t>
-  </si>
-  <si>
-    <t>9032023653356</t>
-  </si>
-  <si>
-    <t>9032033075822</t>
-  </si>
-  <si>
-    <t>205-9001007790944-88</t>
-  </si>
-  <si>
-    <t>Gotovinski kredit</t>
-  </si>
-  <si>
-    <t>0049034095794</t>
-  </si>
-  <si>
-    <t>Stambeni kredit</t>
-  </si>
-  <si>
-    <t>0049005022648</t>
-  </si>
-  <si>
-    <t>KOAR TGR</t>
-  </si>
-  <si>
-    <t>ULICAA</t>
-  </si>
-  <si>
-    <t>Beograd</t>
-  </si>
-  <si>
-    <t>205-9001000243808-47</t>
-  </si>
-  <si>
     <t>ULICAA,BEOGRAD</t>
   </si>
   <si>
@@ -294,6 +306,12 @@
   </si>
   <si>
     <t>4313********5309</t>
+  </si>
+  <si>
+    <t>205-9001005222221-92</t>
+  </si>
+  <si>
+    <t>MILENKA AĆIMOVIĆ</t>
   </si>
 </sst>
 </file>
@@ -920,7 +938,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -930,9 +948,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
@@ -941,9 +956,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center"/>
@@ -1481,59 +1493,59 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AY8"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="7"/>
+  <dimension ref="A1:BB10"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="17.712962962963" style="3" customWidth="1"/>
-    <col min="2" max="2" width="10.5555555555556" style="3" customWidth="1"/>
-    <col min="3" max="3" width="33.5740740740741" style="3" customWidth="1"/>
-    <col min="4" max="4" width="8.88888888888889" style="3"/>
-    <col min="5" max="5" width="22.1111111111111" style="3" customWidth="1"/>
-    <col min="6" max="6" width="33" style="3" customWidth="1"/>
-    <col min="7" max="7" width="23.6666666666667" style="3" customWidth="1"/>
-    <col min="8" max="9" width="33.8888888888889" style="3" customWidth="1"/>
-    <col min="10" max="10" width="23.6666666666667" style="3" customWidth="1"/>
-    <col min="11" max="11" width="28.7407407407407" style="3" customWidth="1"/>
-    <col min="12" max="12" width="24.2222222222222" style="3" customWidth="1"/>
-    <col min="13" max="13" width="27.8888888888889" style="3" customWidth="1"/>
-    <col min="14" max="14" width="28.8611111111111" style="3" customWidth="1"/>
-    <col min="15" max="15" width="24.2222222222222" style="3" customWidth="1"/>
-    <col min="16" max="16" width="23.6666666666667" style="3" customWidth="1"/>
-    <col min="17" max="17" width="31.2222222222222" style="3" customWidth="1"/>
-    <col min="18" max="18" width="19.5555555555556" style="3" customWidth="1"/>
-    <col min="19" max="19" width="21.4444444444444" style="3" customWidth="1"/>
-    <col min="20" max="22" width="24.1111111111111" style="3" customWidth="1"/>
-    <col min="23" max="23" width="25.4259259259259" style="3" customWidth="1"/>
-    <col min="24" max="24" width="24.1111111111111" style="3" customWidth="1"/>
-    <col min="25" max="25" width="25.8796296296296" style="3" customWidth="1"/>
-    <col min="26" max="26" width="24.1111111111111" style="3" customWidth="1"/>
-    <col min="27" max="27" width="32.1851851851852" style="3" customWidth="1"/>
-    <col min="28" max="28" width="21.4444444444444" style="3" customWidth="1"/>
-    <col min="29" max="29" width="32.6666666666667" style="3" customWidth="1"/>
-    <col min="30" max="30" width="17.6666666666667" style="3" customWidth="1"/>
-    <col min="31" max="31" width="23.8888888888889" style="3" customWidth="1"/>
-    <col min="32" max="32" width="26.0092592592593" style="3" customWidth="1"/>
-    <col min="33" max="33" width="23.5555555555556" style="3" customWidth="1"/>
-    <col min="34" max="34" width="26.0092592592593" style="3" customWidth="1"/>
-    <col min="35" max="35" width="23.5555555555556" style="3" customWidth="1"/>
-    <col min="36" max="36" width="31" style="3" customWidth="1"/>
-    <col min="37" max="38" width="32.8888888888889" style="3" customWidth="1"/>
-    <col min="39" max="39" width="29.1111111111111" style="3" customWidth="1"/>
-    <col min="40" max="40" width="33" style="3" customWidth="1"/>
-    <col min="41" max="41" width="37.1111111111111" style="3" customWidth="1"/>
-    <col min="42" max="42" width="31.2222222222222" style="3" customWidth="1"/>
-    <col min="43" max="43" width="18.5555555555556" style="3" customWidth="1"/>
-    <col min="44" max="44" width="16.6666666666667" style="3" customWidth="1"/>
-    <col min="45" max="45" width="14.7777777777778" style="3" customWidth="1"/>
-    <col min="46" max="47" width="23.7777777777778" style="3" customWidth="1"/>
-    <col min="48" max="48" width="37.7777777777778" customWidth="1"/>
-    <col min="49" max="49" width="27.8888888888889" customWidth="1"/>
-    <col min="50" max="50" width="31.7777777777778" customWidth="1"/>
-    <col min="51" max="51" width="27.8888888888889" customWidth="1"/>
-    <col min="52" max="16384" width="8.88888888888889" style="3"/>
+    <col min="1" max="1" width="17.712962962963" customWidth="1"/>
+    <col min="2" max="2" width="10.5555555555556" customWidth="1"/>
+    <col min="3" max="3" width="33.5740740740741" customWidth="1"/>
+    <col min="5" max="6" width="22.1111111111111" customWidth="1"/>
+    <col min="7" max="7" width="33" customWidth="1"/>
+    <col min="8" max="8" width="23.6666666666667" customWidth="1"/>
+    <col min="9" max="10" width="33.8888888888889" customWidth="1"/>
+    <col min="11" max="11" width="23.6666666666667" customWidth="1"/>
+    <col min="12" max="12" width="28.7407407407407" customWidth="1"/>
+    <col min="13" max="13" width="24.2222222222222" customWidth="1"/>
+    <col min="14" max="14" width="27.8888888888889" customWidth="1"/>
+    <col min="15" max="15" width="28.8611111111111" customWidth="1"/>
+    <col min="16" max="16" width="24.2222222222222" customWidth="1"/>
+    <col min="17" max="17" width="23.6666666666667" customWidth="1"/>
+    <col min="18" max="18" width="31.2222222222222" customWidth="1"/>
+    <col min="19" max="19" width="19.5555555555556" customWidth="1"/>
+    <col min="20" max="20" width="21.4444444444444" customWidth="1"/>
+    <col min="21" max="23" width="24.1111111111111" customWidth="1"/>
+    <col min="24" max="24" width="25.4259259259259" customWidth="1"/>
+    <col min="25" max="25" width="24.1111111111111" customWidth="1"/>
+    <col min="26" max="26" width="25.8796296296296" customWidth="1"/>
+    <col min="27" max="27" width="24.1111111111111" customWidth="1"/>
+    <col min="28" max="28" width="32.1851851851852" customWidth="1"/>
+    <col min="29" max="29" width="21.4444444444444" customWidth="1"/>
+    <col min="30" max="30" width="32.6666666666667" customWidth="1"/>
+    <col min="31" max="31" width="17.6666666666667" customWidth="1"/>
+    <col min="32" max="32" width="23.8888888888889" customWidth="1"/>
+    <col min="33" max="33" width="26.0092592592593" customWidth="1"/>
+    <col min="34" max="34" width="23.5555555555556" customWidth="1"/>
+    <col min="35" max="35" width="26.0092592592593" customWidth="1"/>
+    <col min="36" max="36" width="23.5555555555556" customWidth="1"/>
+    <col min="37" max="37" width="31" customWidth="1"/>
+    <col min="38" max="39" width="32.8888888888889" customWidth="1"/>
+    <col min="40" max="40" width="29.1111111111111" customWidth="1"/>
+    <col min="41" max="41" width="33" customWidth="1"/>
+    <col min="42" max="42" width="37.1111111111111" customWidth="1"/>
+    <col min="43" max="43" width="31.2222222222222" customWidth="1"/>
+    <col min="44" max="44" width="18.5555555555556" customWidth="1"/>
+    <col min="45" max="45" width="16.6666666666667" customWidth="1"/>
+    <col min="46" max="46" width="14.7777777777778" customWidth="1"/>
+    <col min="47" max="48" width="23.7777777777778" customWidth="1"/>
+    <col min="49" max="49" width="37.7777777777778" customWidth="1"/>
+    <col min="50" max="50" width="27.8888888888889" customWidth="1"/>
+    <col min="51" max="51" width="31.7777777777778" customWidth="1"/>
+    <col min="52" max="52" width="27.8888888888889" customWidth="1"/>
+    <col min="53" max="53" width="26.6666666666667" customWidth="1"/>
+    <col min="54" max="54" width="34.2222222222222" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:51">
+    <row r="1" s="1" customFormat="1" spans="1:54">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1624,10 +1636,10 @@
       <c r="AD1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="4" t="s">
+      <c r="AE1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AF1" s="3" t="s">
         <v>31</v>
       </c>
       <c r="AG1" s="1" t="s">
@@ -1664,10 +1676,10 @@
         <v>42</v>
       </c>
       <c r="AR1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AS1" s="1" t="s">
         <v>2</v>
-      </c>
-      <c r="AS1" s="1" t="s">
-        <v>43</v>
       </c>
       <c r="AT1" s="1" t="s">
         <v>44</v>
@@ -1675,1102 +1687,1502 @@
       <c r="AU1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="AV1" s="5" t="s">
+      <c r="AV1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="AW1" s="5" t="s">
+      <c r="AW1" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="AX1" s="5" t="s">
+      <c r="AX1" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="AY1" s="5" t="s">
+      <c r="AY1" s="4" t="s">
         <v>49</v>
       </c>
+      <c r="AZ1" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="BA1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="BB1" s="1" t="s">
+        <v>52</v>
+      </c>
     </row>
-    <row r="2" s="2" customFormat="1" spans="1:51">
-      <c r="A2" s="6" t="s">
-        <v>50</v>
+    <row r="2" s="2" customFormat="1" spans="1:54">
+      <c r="A2" s="5" t="s">
+        <v>53</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D2" s="2">
         <v>0</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>57</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="I2" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="M2" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="J2" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>55</v>
-      </c>
       <c r="N2" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="R2" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="U2" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="S2" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="T2" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="U2" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="V2" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="W2" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="X2" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="Y2" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="Z2" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA2" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="AB2" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC2" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="AD2" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="AE2" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="W2" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="X2" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="Y2" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="Z2" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="AA2" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="AB2" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="AC2" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="AD2" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="AE2" s="2" t="s">
+      <c r="AF2" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="AG2" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="AH2" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="AI2" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="AJ2" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="AK2" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="AL2" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="AM2" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="AN2" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="AO2" s="2">
         <v>73</v>
       </c>
-      <c r="AF2" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="AG2" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="AH2" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="AI2" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="AJ2" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="AK2" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="AL2" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="AM2" s="2" t="s">
+      <c r="AP2" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="AQ2" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="AR2" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="AS2" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="AN2" s="2">
-        <v>73</v>
-      </c>
-      <c r="AO2" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="AP2" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="AQ2" s="2" t="s">
+      <c r="AT2" s="2" t="s">
         <v>83</v>
-      </c>
-      <c r="AR2" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="AS2" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="AT2" s="2" t="s">
-        <v>81</v>
       </c>
       <c r="AU2" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="AV2" t="s">
-        <v>85</v>
+      <c r="AV2" s="2" t="s">
+        <v>88</v>
       </c>
       <c r="AW2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="AX2" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="AY2" t="s">
-        <v>88</v>
+        <v>91</v>
+      </c>
+      <c r="AZ2" t="s">
+        <v>92</v>
+      </c>
+      <c r="BA2" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="BB2" s="2" t="s">
+        <v>94</v>
       </c>
     </row>
-    <row r="3" s="2" customFormat="1" spans="1:51">
-      <c r="A3" s="6" t="s">
-        <v>50</v>
+    <row r="3" s="2" customFormat="1" spans="1:54">
+      <c r="A3" s="5" t="s">
+        <v>53</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D3" s="2">
         <v>0</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>57</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="I3" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="M3" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="J3" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>55</v>
-      </c>
       <c r="N3" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="R3" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="U3" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="S3" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="T3" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="U3" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="V3" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="W3" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="X3" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="Y3" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="Z3" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA3" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="AB3" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC3" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="AD3" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="AE3" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="W3" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="X3" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="Y3" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="Z3" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="AA3" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="AB3" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="AC3" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="AD3" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="AE3" s="2" t="s">
+      <c r="AF3" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="AG3" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="AH3" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="AI3" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="AJ3" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="AK3" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="AL3" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="AM3" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="AN3" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="AO3" s="2">
         <v>73</v>
       </c>
-      <c r="AF3" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="AG3" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="AH3" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="AI3" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="AJ3" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="AK3" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="AL3" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="AM3" s="2" t="s">
+      <c r="AP3" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="AQ3" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="AR3" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="AS3" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="AN3" s="2">
-        <v>73</v>
-      </c>
-      <c r="AO3" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="AP3" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="AQ3" s="2" t="s">
+      <c r="AT3" s="2" t="s">
         <v>83</v>
-      </c>
-      <c r="AR3" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="AS3" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="AT3" s="2" t="s">
-        <v>81</v>
       </c>
       <c r="AU3" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="AV3" t="s">
-        <v>85</v>
+      <c r="AV3" s="2" t="s">
+        <v>88</v>
       </c>
       <c r="AW3" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="AX3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="AY3" t="s">
-        <v>88</v>
+        <v>91</v>
+      </c>
+      <c r="AZ3" t="s">
+        <v>92</v>
+      </c>
+      <c r="BA3" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="BB3" s="2" t="s">
+        <v>94</v>
       </c>
     </row>
-    <row r="4" s="2" customFormat="1" spans="1:51">
-      <c r="A4" s="6" t="s">
-        <v>50</v>
+    <row r="4" s="2" customFormat="1" spans="1:54">
+      <c r="A4" s="5" t="s">
+        <v>53</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D4" s="2">
         <v>0</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>57</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="I4" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="M4" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="J4" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>55</v>
-      </c>
       <c r="N4" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="R4" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="S4" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="T4" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="U4" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="S4" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="T4" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="U4" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="V4" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="W4" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="X4" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="Y4" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="Z4" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA4" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="AB4" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC4" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="AD4" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="AE4" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="W4" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="X4" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="Y4" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="Z4" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="AA4" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="AB4" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="AC4" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="AD4" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="AE4" s="2" t="s">
+      <c r="AF4" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="AG4" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="AH4" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="AI4" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="AJ4" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="AK4" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="AL4" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="AM4" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="AN4" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="AO4" s="2">
         <v>73</v>
       </c>
-      <c r="AF4" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="AG4" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="AH4" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="AI4" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="AJ4" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="AK4" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="AL4" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="AM4" s="2" t="s">
+      <c r="AP4" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="AQ4" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="AR4" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="AS4" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="AN4" s="2">
-        <v>73</v>
-      </c>
-      <c r="AO4" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="AP4" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="AQ4" s="2" t="s">
+      <c r="AT4" s="2" t="s">
         <v>83</v>
-      </c>
-      <c r="AR4" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="AS4" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="AT4" s="2" t="s">
-        <v>81</v>
       </c>
       <c r="AU4" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="AV4" t="s">
-        <v>85</v>
+      <c r="AV4" s="2" t="s">
+        <v>88</v>
       </c>
       <c r="AW4" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="AX4" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="AY4" t="s">
-        <v>88</v>
+        <v>91</v>
+      </c>
+      <c r="AZ4" t="s">
+        <v>92</v>
+      </c>
+      <c r="BA4" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="BB4" s="2" t="s">
+        <v>94</v>
       </c>
     </row>
-    <row r="5" s="2" customFormat="1" spans="1:51">
-      <c r="A5" s="6" t="s">
-        <v>50</v>
+    <row r="5" s="2" customFormat="1" spans="1:54">
+      <c r="A5" s="5" t="s">
+        <v>53</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D5" s="2">
         <v>0</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>57</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="I5" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="M5" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="J5" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>55</v>
-      </c>
       <c r="N5" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="R5" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="S5" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="T5" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="U5" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="S5" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="T5" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="U5" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="V5" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="W5" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="X5" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="Y5" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="Z5" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA5" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="AB5" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC5" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="AD5" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="AE5" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="W5" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="X5" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="Y5" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="Z5" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="AA5" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="AB5" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="AC5" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="AD5" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="AE5" s="2" t="s">
+      <c r="AF5" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="AG5" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="AH5" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="AI5" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="AJ5" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="AK5" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="AL5" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="AM5" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="AN5" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="AO5" s="2">
         <v>73</v>
       </c>
-      <c r="AF5" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="AG5" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="AH5" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="AI5" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="AJ5" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="AK5" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="AL5" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="AM5" s="2" t="s">
+      <c r="AP5" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="AQ5" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="AR5" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="AS5" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="AN5" s="2">
-        <v>73</v>
-      </c>
-      <c r="AO5" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="AP5" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="AQ5" s="2" t="s">
+      <c r="AT5" s="2" t="s">
         <v>83</v>
-      </c>
-      <c r="AR5" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="AS5" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="AT5" s="2" t="s">
-        <v>81</v>
       </c>
       <c r="AU5" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="AV5" t="s">
-        <v>85</v>
+      <c r="AV5" s="2" t="s">
+        <v>88</v>
       </c>
       <c r="AW5" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="AX5" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="AY5" t="s">
-        <v>88</v>
+        <v>91</v>
+      </c>
+      <c r="AZ5" t="s">
+        <v>92</v>
+      </c>
+      <c r="BA5" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="BB5" s="2" t="s">
+        <v>94</v>
       </c>
     </row>
-    <row r="6" s="2" customFormat="1" spans="1:51">
-      <c r="A6" s="6" t="s">
-        <v>50</v>
+    <row r="6" s="2" customFormat="1" spans="1:54">
+      <c r="A6" s="5" t="s">
+        <v>53</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D6" s="2">
         <v>0</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>57</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="I6" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="M6" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="J6" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>55</v>
-      </c>
       <c r="N6" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="R6" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="S6" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="T6" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="U6" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="S6" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="T6" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="U6" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="V6" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="W6" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="X6" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="Y6" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="Z6" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA6" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="AB6" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC6" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="AD6" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="AE6" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="W6" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="X6" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="Y6" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="Z6" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="AA6" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="AB6" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="AC6" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="AD6" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="AE6" s="2" t="s">
+      <c r="AF6" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="AG6" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="AH6" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="AI6" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="AJ6" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="AK6" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="AL6" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="AM6" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="AN6" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="AO6" s="2">
         <v>73</v>
       </c>
-      <c r="AF6" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="AG6" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="AH6" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="AI6" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="AJ6" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="AK6" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="AL6" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="AM6" s="2" t="s">
+      <c r="AP6" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="AQ6" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="AR6" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="AS6" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="AN6" s="2">
-        <v>73</v>
-      </c>
-      <c r="AO6" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="AP6" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="AQ6" s="2" t="s">
+      <c r="AT6" s="2" t="s">
         <v>83</v>
-      </c>
-      <c r="AR6" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="AS6" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="AT6" s="2" t="s">
-        <v>81</v>
       </c>
       <c r="AU6" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="AV6" t="s">
-        <v>85</v>
+      <c r="AV6" s="2" t="s">
+        <v>88</v>
       </c>
       <c r="AW6" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="AX6" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="AY6" t="s">
-        <v>88</v>
+        <v>91</v>
+      </c>
+      <c r="AZ6" t="s">
+        <v>92</v>
+      </c>
+      <c r="BA6" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="BB6" s="2" t="s">
+        <v>94</v>
       </c>
     </row>
-    <row r="7" s="2" customFormat="1" spans="1:51">
-      <c r="A7" s="6" t="s">
-        <v>50</v>
+    <row r="7" s="2" customFormat="1" spans="1:54">
+      <c r="A7" s="5" t="s">
+        <v>53</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D7" s="2">
         <v>0</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>57</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="I7" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="M7" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="J7" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>55</v>
-      </c>
       <c r="N7" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="R7" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="S7" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="T7" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="U7" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="S7" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="T7" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="U7" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="V7" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="W7" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="X7" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="Y7" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="Z7" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA7" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="AB7" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC7" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="AD7" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="AE7" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="W7" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="X7" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="Y7" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="Z7" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="AA7" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="AB7" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="AC7" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="AD7" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="AE7" s="2" t="s">
+      <c r="AF7" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="AG7" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="AH7" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="AI7" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="AJ7" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="AK7" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="AL7" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="AM7" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="AN7" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="AO7" s="2">
         <v>73</v>
       </c>
-      <c r="AF7" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="AG7" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="AH7" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="AI7" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="AJ7" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="AK7" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="AL7" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="AM7" s="2" t="s">
+      <c r="AP7" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="AQ7" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="AR7" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="AS7" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="AN7" s="2">
-        <v>73</v>
-      </c>
-      <c r="AO7" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="AP7" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="AQ7" s="2" t="s">
+      <c r="AT7" s="2" t="s">
         <v>83</v>
-      </c>
-      <c r="AR7" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="AS7" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="AT7" s="2" t="s">
-        <v>81</v>
       </c>
       <c r="AU7" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="AV7" t="s">
-        <v>85</v>
+      <c r="AV7" s="2" t="s">
+        <v>88</v>
       </c>
       <c r="AW7" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="AX7" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="AY7" t="s">
-        <v>88</v>
+        <v>91</v>
+      </c>
+      <c r="AZ7" t="s">
+        <v>92</v>
+      </c>
+      <c r="BA7" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="BB7" s="2" t="s">
+        <v>94</v>
       </c>
     </row>
-    <row r="8" s="2" customFormat="1" spans="1:51">
-      <c r="A8" s="6" t="s">
-        <v>50</v>
+    <row r="8" s="2" customFormat="1" spans="1:54">
+      <c r="A8" s="5" t="s">
+        <v>53</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D8" s="2">
         <v>0</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>57</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="I8" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="M8" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="J8" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>55</v>
-      </c>
       <c r="N8" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="R8" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="S8" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="T8" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="U8" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="S8" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="T8" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="U8" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="V8" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="W8" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="X8" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="Y8" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="Z8" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA8" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="AB8" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC8" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="AD8" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="AE8" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="W8" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="X8" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="Y8" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="Z8" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="AA8" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="AB8" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="AC8" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="AD8" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="AE8" s="2" t="s">
+      <c r="AF8" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="AG8" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="AH8" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="AI8" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="AJ8" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="AK8" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="AL8" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="AM8" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="AN8" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="AO8" s="2">
         <v>73</v>
       </c>
-      <c r="AF8" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="AG8" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="AH8" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="AI8" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="AJ8" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="AK8" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="AL8" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="AM8" s="2" t="s">
+      <c r="AP8" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="AQ8" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="AR8" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="AS8" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="AN8" s="2">
-        <v>73</v>
-      </c>
-      <c r="AO8" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="AP8" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="AQ8" s="2" t="s">
+      <c r="AT8" s="2" t="s">
         <v>83</v>
-      </c>
-      <c r="AR8" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="AS8" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="AT8" s="2" t="s">
-        <v>81</v>
       </c>
       <c r="AU8" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="AV8" t="s">
+      <c r="AV8" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="AW8" t="s">
+        <v>89</v>
+      </c>
+      <c r="AX8" t="s">
+        <v>90</v>
+      </c>
+      <c r="AY8" t="s">
+        <v>91</v>
+      </c>
+      <c r="AZ8" t="s">
+        <v>92</v>
+      </c>
+      <c r="BA8" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="BB8" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="9" s="2" customFormat="1" spans="1:54">
+      <c r="A9" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D9" s="2">
+        <v>0</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q9" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="R9" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="S9" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="T9" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="U9" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="V9" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="W9" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="X9" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="Y9" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="Z9" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA9" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="AB9" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC9" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="AD9" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="AE9" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="AF9" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="AG9" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="AH9" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="AI9" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="AJ9" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="AK9" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="AL9" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="AM9" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="AN9" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="AO9" s="2">
+        <v>73</v>
+      </c>
+      <c r="AP9" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="AW8" t="s">
+      <c r="AQ9" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="AX8" t="s">
+      <c r="AR9" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="AY8" t="s">
+      <c r="AS9" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="AT9" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="AU9" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="AV9" s="2" t="s">
         <v>88</v>
+      </c>
+      <c r="AW9" t="s">
+        <v>89</v>
+      </c>
+      <c r="AX9" t="s">
+        <v>90</v>
+      </c>
+      <c r="AY9" t="s">
+        <v>91</v>
+      </c>
+      <c r="AZ9" t="s">
+        <v>92</v>
+      </c>
+      <c r="BA9" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="BB9" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="10" s="2" customFormat="1" spans="1:54">
+      <c r="A10" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D10" s="2">
+        <v>0</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="N10" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="O10" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="P10" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q10" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="R10" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="S10" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="T10" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="U10" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="V10" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="W10" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="X10" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="Y10" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="Z10" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA10" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="AB10" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC10" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="AD10" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="AE10" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="AF10" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="AG10" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="AH10" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="AI10" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="AJ10" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="AK10" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="AL10" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="AM10" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="AN10" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="AO10" s="2">
+        <v>73</v>
+      </c>
+      <c r="AP10" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="AQ10" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="AR10" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="AS10" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="AT10" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="AU10" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="AV10" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="AW10" t="s">
+        <v>89</v>
+      </c>
+      <c r="AX10" t="s">
+        <v>90</v>
+      </c>
+      <c r="AY10" t="s">
+        <v>91</v>
+      </c>
+      <c r="AZ10" t="s">
+        <v>92</v>
+      </c>
+      <c r="BA10" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="BB10" s="2" t="s">
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -2782,6 +3194,8 @@
     <hyperlink ref="A6" r:id="rId1" display="mirko.lekic@ibank" tooltip="mailto:mirko.lekic@ibank"/>
     <hyperlink ref="A7" r:id="rId1" display="mirko.lekic@ibank" tooltip="mailto:mirko.lekic@ibank"/>
     <hyperlink ref="A8" r:id="rId1" display="mirko.lekic@ibank" tooltip="mailto:mirko.lekic@ibank"/>
+    <hyperlink ref="A9" r:id="rId1" display="mirko.lekic@ibank" tooltip="mailto:mirko.lekic@ibank"/>
+    <hyperlink ref="A10" r:id="rId1" display="mirko.lekic@ibank" tooltip="mailto:mirko.lekic@ibank"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
